--- a/Lab1_D5Report/analysis/alpha/alpha.xlsx
+++ b/Lab1_D5Report/analysis/alpha/alpha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\APLabR_TaLEs\Lab1_D5Report\analysis\alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5469F850-B287-40A9-9065-DD77BEAD32AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E12E85F-E6DD-493D-8D0F-4E9F67322AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19103" yWindow="-172" windowWidth="19395" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="176" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -212,7 +212,7 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -500,9 +500,9 @@
   <cols>
     <col min="10" max="10" width="21.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.77734375" customWidth="1"/>
-    <col min="15" max="15" width="16.88671875" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" customWidth="1"/>
+    <col min="15" max="15" width="13.109375" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -518,7 +518,7 @@
       </c>
       <c r="H1">
         <f>SLOPE(C2:C3,B2:B3)</f>
-        <v>1.1077643908969195E-2</v>
+        <v>9.3767705382436246E-3</v>
       </c>
       <c r="K1" t="s">
         <v>17</v>
@@ -548,26 +548,26 @@
       </c>
       <c r="H2">
         <f>INTERCEPT(C2:C3,B2:B3)</f>
-        <v>-4.1105629183400128</v>
+        <v>-2.6370963172804514</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="K2">
         <f>B15*(C4*1000)^C15</f>
-        <v>272.38412073774549</v>
+        <v>326.23984862149621</v>
       </c>
       <c r="L2">
         <f>D15/((C4*1000)/1000)</f>
-        <v>25.137920979305161</v>
+        <v>18.834799563341715</v>
       </c>
       <c r="M2">
         <f>E15/((C4*1000)/1000)</f>
-        <v>5.5006391639617416E-2</v>
+        <v>4.1214003420879025E-2</v>
       </c>
       <c r="N2">
         <f>F15*(C4*1000)/1000</f>
-        <v>7.9245336224899807</v>
+        <v>10.576502252124648</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -575,7 +575,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>836.42</v>
+        <v>831</v>
       </c>
       <c r="C3">
         <v>5.1550000000000002</v>
@@ -585,11 +585,11 @@
       </c>
       <c r="K3">
         <f>B16*($C$5*1000)^C16</f>
-        <v>97.149457072229424</v>
+        <v>101.21663916651782</v>
       </c>
       <c r="L3">
         <f>D16/(($C$5*1000)/1000)</f>
-        <v>7.1017323920888717</v>
+        <v>6.3888510574648381</v>
       </c>
       <c r="M3">
         <f>E16/((1000)/1000)</f>
@@ -597,7 +597,7 @@
       </c>
       <c r="N3">
         <f>F16*($C$5*1000)/1000</f>
-        <v>25.875245623828683</v>
+        <v>28.76245953257791</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -605,30 +605,30 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>535.17999999999995</v>
+        <v>540</v>
       </c>
       <c r="C4">
         <f>$H$1*B4+$H$2</f>
-        <v>1.8179705488621201</v>
+        <v>2.4263597733711055</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K5" si="0">B17*$C$5^C17</f>
-        <v>1.568628676412045</v>
+        <v>1.6386101074618367</v>
       </c>
       <c r="L4">
         <f t="shared" ref="L4:L5" si="1">D17/($C$5/1000)</f>
-        <v>2137.624539071553</v>
+        <v>1923.0469472664934</v>
       </c>
       <c r="M4">
         <f t="shared" ref="M4:M5" si="2">E17/($C$5/1000)</f>
-        <v>2727.9425295579313</v>
+        <v>2454.1080334263588</v>
       </c>
       <c r="N4">
         <f t="shared" ref="N4:N5" si="3">F17*$C$5/1000</f>
-        <v>8.3585492556894347E-3</v>
+        <v>9.2912136260623248E-3</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -636,30 +636,30 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>663.3</v>
+        <v>665</v>
       </c>
       <c r="C5">
         <f>$H$1*B5+$H$2</f>
-        <v>3.2372382864792542</v>
+        <v>3.5984560906515588</v>
       </c>
       <c r="J5" t="s">
         <v>24</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>3.294927434033061</v>
+        <v>3.4834990649860216</v>
       </c>
       <c r="L5">
         <f t="shared" si="1"/>
-        <v>11463.474948691523</v>
+        <v>10312.756100153118</v>
       </c>
       <c r="M5">
         <f t="shared" si="2"/>
-        <v>4707.7164704408187</v>
+        <v>4235.1496353094453</v>
       </c>
       <c r="N5">
         <f t="shared" si="3"/>
-        <v>9.0772161552878285E-3</v>
+        <v>1.0090070878186971E-2</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -718,25 +718,25 @@
       </c>
       <c r="J15">
         <f>(K2*(L2*LN(1 + M2 + N2)))/(K2 + L2 *LN(1 + M2 + N2))*10^-15</f>
-        <v>4.5882164200194001E-14</v>
+        <v>4.0463612114942605E-14</v>
       </c>
       <c r="K15" s="1">
         <v>6.0199999999999998E+22</v>
       </c>
       <c r="L15" s="1">
         <f>-J15*K15</f>
-        <v>-2762106284.8516788</v>
+        <v>-2435909449.3195448</v>
       </c>
       <c r="N15" t="s">
         <v>26</v>
       </c>
       <c r="O15">
         <f>1000000*(C5-C2)/L19</f>
-        <v>3.54404368287475E-3</v>
+        <v>3.1607936281492586E-3</v>
       </c>
       <c r="P15">
         <f>O15*10000</f>
-        <v>35.440436828747501</v>
+        <v>31.607936281492584</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -763,25 +763,25 @@
       </c>
       <c r="J16">
         <f>(K3*(L3*LN(1 + M3 + N3)))/(K3 + L3 *LN(1 + M3 + N3))*10^-15</f>
-        <v>2.2508148696199131E-14</v>
+        <v>2.1093185899673165E-14</v>
       </c>
       <c r="K16" s="1">
         <v>4.3581999999999996E+22</v>
       </c>
       <c r="L16" s="1">
         <f>-J16*K16</f>
-        <v>-980950136.47775042</v>
+        <v>-919283227.87955582</v>
       </c>
       <c r="N16" t="s">
         <v>27</v>
       </c>
       <c r="O16" s="1">
         <f>1000000*(C4-C2)/L15</f>
-        <v>1.3279827323280746E-3</v>
+        <v>1.2560566352265619E-3</v>
       </c>
       <c r="P16" s="1">
         <f>O16*10000</f>
-        <v>13.279827323280745</v>
+        <v>12.560566352265619</v>
       </c>
       <c r="Q16" s="1"/>
     </row>
@@ -809,14 +809,14 @@
       </c>
       <c r="J17">
         <f>(K4*(L4*LN(1 + M4 + N4)))/(K4 + L4 *LN(1 + M4 + N4))*10^-15</f>
-        <v>1.5684831974172552E-15</v>
+        <v>1.638431257305392E-15</v>
       </c>
       <c r="K17" s="1">
         <v>3.4865999999999999E+22</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" ref="L17:L18" si="4">-J17*K17</f>
-        <v>-54686735.161150016</v>
+        <v>-57125544.217209794</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -843,14 +843,14 @@
       </c>
       <c r="J18">
         <f>(K5*(L5*LN(1 + M5 + N5)))/(K5 + L5 *LN(1 + M5 + N5))*10^-15</f>
-        <v>3.2948154553204379E-15</v>
+        <v>3.4833581753153805E-15</v>
       </c>
       <c r="K18" s="1">
         <v>1.7433E+22</v>
       </c>
       <c r="L18" s="2">
         <f t="shared" si="4"/>
-        <v>-57438517.83260119</v>
+        <v>-60725383.070273027</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -859,7 +859,7 @@
       </c>
       <c r="L19">
         <f>(10*12*L16+8*1*L17+4*16*L18)/(10*12+8*1+4*16)</f>
-        <v>-634518621.87450898</v>
+        <v>-597174042.79053032</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
